--- a/Lab/Lab2/Tabela_inicial.xlsx
+++ b/Lab/Lab2/Tabela_inicial.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25906"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -15,11 +15,7 @@
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Folha1!$B$3:$B$17</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Folha1!$G$3:$G$17</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -55,7 +53,13 @@
     <t>Ficheiro</t>
   </si>
   <si>
+    <t>Nós</t>
+  </si>
+  <si>
     <t>Pares</t>
+  </si>
+  <si>
+    <t>Ligações</t>
   </si>
   <si>
     <t>Find</t>
@@ -111,18 +115,12 @@
   <si>
     <t>z500000.txt</t>
   </si>
-  <si>
-    <t>Nós</t>
-  </si>
-  <si>
-    <t>Ligações</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -551,21 +549,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -590,9 +573,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -605,14 +585,32 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -673,7 +671,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="pt-PT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -757,7 +755,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="pt-PT"/>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -943,7 +941,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="pt-PT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1227278896"/>
@@ -1005,7 +1003,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="pt-PT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1227278480"/>
@@ -1047,7 +1045,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="pt-PT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -1084,7 +1082,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="pt-PT"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1132,7 +1130,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="pt-PT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1223,7 +1221,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="pt-PT"/>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -1436,7 +1434,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="pt-PT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1132594112"/>
@@ -1475,7 +1473,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="pt-PT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -1519,7 +1517,7 @@
           <a:cs typeface="+mn-cs"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="pt-PT"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1567,7 +1565,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="pt-PT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1650,7 +1648,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="pt-PT"/>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -1833,7 +1831,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="pt-PT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1231067712"/>
@@ -1893,7 +1891,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="pt-PT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1231062720"/>
@@ -1932,7 +1930,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="pt-PT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -1976,7 +1974,7 @@
           <a:cs typeface="+mn-cs"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="pt-PT"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2027,7 +2025,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="pt-PT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2110,7 +2108,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="pt-PT"/>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -2296,7 +2294,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="pt-PT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1420986208"/>
@@ -2358,7 +2356,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="pt-PT"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1420980384"/>
@@ -2400,7 +2398,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="pt-PT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -2437,7 +2435,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="pt-PT"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -5085,7 +5083,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.5703125" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" customWidth="1"/>
@@ -5100,85 +5098,85 @@
     <col min="16" max="16" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24"/>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="11" t="s">
+    <row r="1" spans="1:18" ht="19.5" thickTop="1" thickBot="1">
+      <c r="A1" s="26"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="12"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="11" t="s">
+      <c r="F1" s="29"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="11" t="s">
+      <c r="I1" s="29"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="12"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="14" t="s">
+      <c r="L1" s="29"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="14"/>
-      <c r="P1" s="15"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="32"/>
     </row>
-    <row r="2" spans="1:18" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
+    <row r="2" spans="1:18" ht="19.5" thickTop="1" thickBot="1">
+      <c r="A2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="16" t="s">
+      <c r="B2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="16" t="s">
+      <c r="C2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="D2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="E2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="16" t="s">
+      <c r="F2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="L2" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="M2" s="16" t="s">
+      <c r="I2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="P2" s="16" t="s">
+      <c r="L2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="11" t="s">
         <v>8</v>
       </c>
+      <c r="O2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>9</v>
+    <row r="3" spans="1:18" ht="19.5" thickTop="1" thickBot="1">
+      <c r="A3" s="13" t="s">
+        <v>11</v>
       </c>
       <c r="B3" s="1">
         <v>10</v>
@@ -5234,9 +5232,9 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
-        <v>10</v>
+    <row r="4" spans="1:18" ht="18.75" thickBot="1">
+      <c r="A4" s="13" t="s">
+        <v>12</v>
       </c>
       <c r="B4" s="1">
         <v>20</v>
@@ -5292,9 +5290,9 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
-        <v>11</v>
+    <row r="5" spans="1:18" ht="18.75" thickBot="1">
+      <c r="A5" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="B5" s="1">
         <v>50</v>
@@ -5350,9 +5348,9 @@
         <v>10.74</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
-        <v>12</v>
+    <row r="6" spans="1:18" ht="18.75" thickBot="1">
+      <c r="A6" s="13" t="s">
+        <v>14</v>
       </c>
       <c r="B6" s="1">
         <v>100</v>
@@ -5408,9 +5406,9 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
-        <v>13</v>
+    <row r="7" spans="1:18" ht="18.75" thickBot="1">
+      <c r="A7" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="B7" s="1">
         <v>200</v>
@@ -5466,9 +5464,9 @@
         <v>10.87</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
-        <v>14</v>
+    <row r="8" spans="1:18" ht="18.75" thickBot="1">
+      <c r="A8" s="13" t="s">
+        <v>16</v>
       </c>
       <c r="B8" s="1">
         <v>500</v>
@@ -5524,9 +5522,9 @@
         <v>11.47</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
-        <v>15</v>
+    <row r="9" spans="1:18" ht="18.75" thickBot="1">
+      <c r="A9" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="B9" s="1">
         <v>1000</v>
@@ -5582,9 +5580,9 @@
         <v>11.407</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>16</v>
+    <row r="10" spans="1:18" ht="18.75" thickBot="1">
+      <c r="A10" s="13" t="s">
+        <v>18</v>
       </c>
       <c r="B10" s="1">
         <v>2000</v>
@@ -5640,9 +5638,9 @@
         <v>11.673999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
-        <v>17</v>
+    <row r="11" spans="1:18" ht="18.75" thickBot="1">
+      <c r="A11" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="B11" s="1">
         <v>5000</v>
@@ -5698,14 +5696,14 @@
         <v>11.597</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="26">
+    <row r="12" spans="1:18" ht="19.5" thickBot="1">
+      <c r="A12" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="20">
         <v>10000</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="20">
         <v>10000</v>
       </c>
       <c r="D12" s="4">
@@ -5756,9 +5754,9 @@
         <v>11.6723</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
-        <v>19</v>
+    <row r="13" spans="1:18" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A13" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="B13" s="1">
         <v>20000</v>
@@ -5814,9 +5812,9 @@
         <v>11.675599999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
-        <v>20</v>
+    <row r="14" spans="1:18" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A14" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="B14" s="1">
         <v>50000</v>
@@ -5872,9 +5870,9 @@
         <v>11.77608</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="s">
-        <v>21</v>
+    <row r="15" spans="1:18" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A15" s="15" t="s">
+        <v>23</v>
       </c>
       <c r="B15" s="1">
         <v>100000</v>
@@ -5930,9 +5928,9 @@
         <v>11.798220000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="21" t="s">
-        <v>22</v>
+    <row r="16" spans="1:18" ht="18.75" thickBot="1">
+      <c r="A16" s="16" t="s">
+        <v>24</v>
       </c>
       <c r="B16" s="3">
         <v>200000</v>
@@ -5988,26 +5986,26 @@
         <v>11.81967</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="32">
+    <row r="17" spans="1:18" ht="18.75" thickBot="1">
+      <c r="A17" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="25">
         <v>500000</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="24">
         <v>500000</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="18">
         <v>419003</v>
       </c>
       <c r="E17" s="8">
         <v>1000000</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="21">
         <v>237042719811</v>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="22">
         <f t="shared" si="4"/>
         <v>237043719811</v>
       </c>
@@ -6017,7 +6015,7 @@
       <c r="I17" s="9">
         <v>419003</v>
       </c>
-      <c r="J17" s="29">
+      <c r="J17" s="19">
         <f t="shared" si="0"/>
         <v>11002310151</v>
       </c>
@@ -6046,8 +6044,8 @@
         <v>11.799122000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="J18" s="30"/>
+    <row r="18" spans="1:18" ht="15.75" thickTop="1">
+      <c r="J18" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="5">
